--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
@@ -6944,7 +6944,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251018_201521.xlsx
@@ -4856,7 +4856,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
